--- a/DataframeAcao.xlsx
+++ b/DataframeAcao.xlsx
@@ -21,9 +21,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
-    <t>Data</t>
-  </si>
-  <si>
     <t>Preco</t>
   </si>
   <si>
@@ -35,14 +32,14 @@
   <si>
     <t>DirecaoPreco</t>
   </si>
+  <si>
+    <t>Dia</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
-  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -95,12 +92,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -408,7 +408,7 @@
   <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="7.5546875" bestFit="1" customWidth="1"/>
@@ -416,25 +416,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>46082</v>
+      <c r="A2" s="3">
+        <v>1</v>
       </c>
       <c r="B2">
         <v>101.35844985184001</v>
@@ -451,8 +451,8 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>46083</v>
+      <c r="A3" s="3">
+        <v>2</v>
       </c>
       <c r="B3">
         <v>102.5061383899407</v>
@@ -469,8 +469,8 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>46084</v>
+      <c r="A4" s="3">
+        <v>3</v>
       </c>
       <c r="B4">
         <v>104.5291682463488</v>
@@ -487,8 +487,8 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>46085</v>
+      <c r="A5" s="3">
+        <v>4</v>
       </c>
       <c r="B5">
         <v>104.7950148716254</v>
@@ -505,8 +505,8 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>46086</v>
+      <c r="A6" s="3">
+        <v>5</v>
       </c>
       <c r="B6">
         <v>105.0608779146763</v>
@@ -523,8 +523,8 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>46087</v>
+      <c r="A7" s="3">
+        <v>6</v>
       </c>
       <c r="B7">
         <v>107.1400907301836</v>
@@ -541,8 +541,8 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>46088</v>
+      <c r="A8" s="3">
+        <v>7</v>
       </c>
       <c r="B8">
         <v>108.4075254593366</v>
@@ -559,8 +559,8 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
-        <v>46089</v>
+      <c r="A9" s="3">
+        <v>8</v>
       </c>
       <c r="B9">
         <v>108.4380510734016</v>
@@ -577,8 +577,8 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>46090</v>
+      <c r="A10" s="3">
+        <v>9</v>
       </c>
       <c r="B10">
         <v>109.4806111169876</v>
@@ -595,8 +595,8 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>46091</v>
+      <c r="A11" s="3">
+        <v>10</v>
       </c>
       <c r="B11">
         <v>109.5171934241751</v>
@@ -613,8 +613,8 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <v>46092</v>
+      <c r="A12" s="3">
+        <v>11</v>
       </c>
       <c r="B12">
         <v>109.5514636706048</v>
@@ -631,8 +631,8 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>46093</v>
+      <c r="A13" s="3">
+        <v>12</v>
       </c>
       <c r="B13">
         <v>110.2934259421709</v>
@@ -649,8 +649,8 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
-        <v>46094</v>
+      <c r="A14" s="3">
+        <v>13</v>
       </c>
       <c r="B14">
         <v>108.8801456975131</v>
@@ -667,8 +667,8 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
-        <v>46095</v>
+      <c r="A15" s="3">
+        <v>14</v>
       </c>
       <c r="B15">
         <v>107.655227865</v>
@@ -685,8 +685,8 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
-        <v>46096</v>
+      <c r="A16" s="3">
+        <v>15</v>
       </c>
       <c r="B16">
         <v>107.5929403357591</v>
@@ -703,8 +703,8 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <v>46097</v>
+      <c r="A17" s="3">
+        <v>16</v>
       </c>
       <c r="B17">
         <v>107.0801092154247</v>
@@ -721,8 +721,8 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
-        <v>46098</v>
+      <c r="A18" s="3">
+        <v>17</v>
       </c>
       <c r="B18">
         <v>107.8943565480199</v>
@@ -739,8 +739,8 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
-        <v>46099</v>
+      <c r="A19" s="3">
+        <v>18</v>
       </c>
       <c r="B19">
         <v>107.4863324724987</v>
@@ -757,8 +757,8 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
-        <v>46100</v>
+      <c r="A20" s="3">
+        <v>19</v>
       </c>
       <c r="B20">
         <v>106.5740287711634</v>
@@ -775,8 +775,8 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
-        <v>46101</v>
+      <c r="A21" s="3">
+        <v>20</v>
       </c>
       <c r="B21">
         <v>108.53967754008499</v>
@@ -793,8 +793,8 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
-        <v>46102</v>
+      <c r="A22" s="3">
+        <v>21</v>
       </c>
       <c r="B22">
         <v>108.81390123959839</v>
@@ -811,8 +811,8 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
-        <v>46103</v>
+      <c r="A23" s="3">
+        <v>22</v>
       </c>
       <c r="B23">
         <v>109.3814294442864</v>
@@ -829,8 +829,8 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
-        <v>46104</v>
+      <c r="A24" s="3">
+        <v>23</v>
       </c>
       <c r="B24">
         <v>108.4566812580729</v>
@@ -847,8 +847,8 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
-        <v>46105</v>
+      <c r="A25" s="3">
+        <v>24</v>
       </c>
       <c r="B25">
         <v>108.4122985335477</v>
@@ -865,8 +865,8 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
-        <v>46106</v>
+      <c r="A26" s="3">
+        <v>25</v>
       </c>
       <c r="B26">
         <v>109.0232211232576</v>
@@ -883,8 +883,8 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="2">
-        <v>46107</v>
+      <c r="A27" s="3">
+        <v>26</v>
       </c>
       <c r="B27">
         <v>108.3722275458353</v>
@@ -901,8 +901,8 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
-        <v>46108</v>
+      <c r="A28" s="3">
+        <v>27</v>
       </c>
       <c r="B28">
         <v>109.247925564181</v>
@@ -919,8 +919,8 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="2">
-        <v>46109</v>
+      <c r="A29" s="3">
+        <v>28</v>
       </c>
       <c r="B29">
         <v>117.342167037574</v>
@@ -937,8 +937,8 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="2">
-        <v>46110</v>
+      <c r="A30" s="3">
+        <v>29</v>
       </c>
       <c r="B30">
         <v>124.91242767799569</v>
@@ -955,8 +955,8 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="2">
-        <v>46111</v>
+      <c r="A31" s="3">
+        <v>30</v>
       </c>
       <c r="B31">
         <v>132.48268831841699</v>

--- a/DataframeAcao.xlsx
+++ b/DataframeAcao.xlsx
@@ -439,9 +439,9 @@
       <c r="B2">
         <v>101.35844985184001</v>
       </c>
-      <c r="C2">
-        <f>IF(B3&gt;B2,1,0)</f>
-        <v>1</v>
+      <c r="C2" t="str">
+        <f>IF(B3&gt;B2,"Subiu","Caiu")</f>
+        <v>Subiu</v>
       </c>
       <c r="D2">
         <v>4499</v>
@@ -457,9 +457,9 @@
       <c r="B3">
         <v>102.5061383899407</v>
       </c>
-      <c r="C3">
-        <f t="shared" ref="C3:C31" si="0">IF(B4&gt;B3,1,0)</f>
-        <v>1</v>
+      <c r="C3" t="str">
+        <f t="shared" ref="C3:C31" si="0">IF(B4&gt;B3,"Subiu","Caiu")</f>
+        <v>Subiu</v>
       </c>
       <c r="D3">
         <v>3556</v>
@@ -475,9 +475,9 @@
       <c r="B4">
         <v>104.5291682463488</v>
       </c>
-      <c r="C4">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="C4" t="str">
+        <f t="shared" si="0"/>
+        <v>Subiu</v>
       </c>
       <c r="D4">
         <v>1775</v>
@@ -493,9 +493,9 @@
       <c r="B5">
         <v>104.7950148716254</v>
       </c>
-      <c r="C5">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="C5" t="str">
+        <f t="shared" si="0"/>
+        <v>Subiu</v>
       </c>
       <c r="D5">
         <v>1034</v>
@@ -511,9 +511,9 @@
       <c r="B6">
         <v>105.0608779146763</v>
       </c>
-      <c r="C6">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="C6" t="str">
+        <f t="shared" si="0"/>
+        <v>Subiu</v>
       </c>
       <c r="D6">
         <v>3253</v>
@@ -529,9 +529,9 @@
       <c r="B7">
         <v>107.1400907301836</v>
       </c>
-      <c r="C7">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="C7" t="str">
+        <f t="shared" si="0"/>
+        <v>Subiu</v>
       </c>
       <c r="D7">
         <v>4152</v>
@@ -547,9 +547,9 @@
       <c r="B8">
         <v>108.4075254593366</v>
       </c>
-      <c r="C8">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="C8" t="str">
+        <f t="shared" si="0"/>
+        <v>Subiu</v>
       </c>
       <c r="D8">
         <v>2955</v>
@@ -565,9 +565,9 @@
       <c r="B9">
         <v>108.4380510734016</v>
       </c>
-      <c r="C9">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="C9" t="str">
+        <f t="shared" si="0"/>
+        <v>Subiu</v>
       </c>
       <c r="D9">
         <v>2585</v>
@@ -583,9 +583,9 @@
       <c r="B10">
         <v>109.4806111169876</v>
       </c>
-      <c r="C10">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="C10" t="str">
+        <f t="shared" si="0"/>
+        <v>Subiu</v>
       </c>
       <c r="D10">
         <v>4943</v>
@@ -601,9 +601,9 @@
       <c r="B11">
         <v>109.5171934241751</v>
       </c>
-      <c r="C11">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="C11" t="str">
+        <f t="shared" si="0"/>
+        <v>Subiu</v>
       </c>
       <c r="D11">
         <v>4459</v>
@@ -619,9 +619,9 @@
       <c r="B12">
         <v>109.5514636706048</v>
       </c>
-      <c r="C12">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="C12" t="str">
+        <f t="shared" si="0"/>
+        <v>Subiu</v>
       </c>
       <c r="D12">
         <v>4073</v>
@@ -637,9 +637,9 @@
       <c r="B13">
         <v>110.2934259421709</v>
       </c>
-      <c r="C13">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="C13" t="str">
+        <f t="shared" si="0"/>
+        <v>Caiu</v>
       </c>
       <c r="D13">
         <v>2021</v>
@@ -655,9 +655,9 @@
       <c r="B14">
         <v>108.8801456975131</v>
       </c>
-      <c r="C14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="C14" t="str">
+        <f t="shared" si="0"/>
+        <v>Caiu</v>
       </c>
       <c r="D14">
         <v>4461</v>
@@ -673,9 +673,9 @@
       <c r="B15">
         <v>107.655227865</v>
       </c>
-      <c r="C15">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="C15" t="str">
+        <f t="shared" si="0"/>
+        <v>Caiu</v>
       </c>
       <c r="D15">
         <v>3613</v>
@@ -691,9 +691,9 @@
       <c r="B16">
         <v>107.5929403357591</v>
       </c>
-      <c r="C16">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="C16" t="str">
+        <f t="shared" si="0"/>
+        <v>Caiu</v>
       </c>
       <c r="D16">
         <v>2129</v>
@@ -709,9 +709,9 @@
       <c r="B17">
         <v>107.0801092154247</v>
       </c>
-      <c r="C17">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="C17" t="str">
+        <f t="shared" si="0"/>
+        <v>Subiu</v>
       </c>
       <c r="D17">
         <v>4843</v>
@@ -727,9 +727,9 @@
       <c r="B18">
         <v>107.8943565480199</v>
       </c>
-      <c r="C18">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="C18" t="str">
+        <f t="shared" si="0"/>
+        <v>Caiu</v>
       </c>
       <c r="D18">
         <v>4893</v>
@@ -745,9 +745,9 @@
       <c r="B19">
         <v>107.4863324724987</v>
       </c>
-      <c r="C19">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="C19" t="str">
+        <f t="shared" si="0"/>
+        <v>Caiu</v>
       </c>
       <c r="D19">
         <v>2500</v>
@@ -763,9 +763,9 @@
       <c r="B20">
         <v>106.5740287711634</v>
       </c>
-      <c r="C20">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="C20" t="str">
+        <f t="shared" si="0"/>
+        <v>Subiu</v>
       </c>
       <c r="D20">
         <v>1702</v>
@@ -781,9 +781,9 @@
       <c r="B21">
         <v>108.53967754008499</v>
       </c>
-      <c r="C21">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="C21" t="str">
+        <f t="shared" si="0"/>
+        <v>Subiu</v>
       </c>
       <c r="D21">
         <v>3449</v>
@@ -799,9 +799,9 @@
       <c r="B22">
         <v>108.81390123959839</v>
       </c>
-      <c r="C22">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="C22" t="str">
+        <f t="shared" si="0"/>
+        <v>Subiu</v>
       </c>
       <c r="D22">
         <v>3777</v>
@@ -817,9 +817,9 @@
       <c r="B23">
         <v>109.3814294442864</v>
       </c>
-      <c r="C23">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="C23" t="str">
+        <f t="shared" si="0"/>
+        <v>Caiu</v>
       </c>
       <c r="D23">
         <v>2579</v>
@@ -835,9 +835,9 @@
       <c r="B24">
         <v>108.4566812580729</v>
       </c>
-      <c r="C24">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="C24" t="str">
+        <f t="shared" si="0"/>
+        <v>Caiu</v>
       </c>
       <c r="D24">
         <v>1161</v>
@@ -853,9 +853,9 @@
       <c r="B25">
         <v>108.4122985335477</v>
       </c>
-      <c r="C25">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="C25" t="str">
+        <f t="shared" si="0"/>
+        <v>Subiu</v>
       </c>
       <c r="D25">
         <v>1201</v>
@@ -871,9 +871,9 @@
       <c r="B26">
         <v>109.0232211232576</v>
       </c>
-      <c r="C26">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="C26" t="str">
+        <f t="shared" si="0"/>
+        <v>Caiu</v>
       </c>
       <c r="D26">
         <v>2981</v>
@@ -889,9 +889,9 @@
       <c r="B27">
         <v>108.3722275458353</v>
       </c>
-      <c r="C27">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="C27" t="str">
+        <f t="shared" si="0"/>
+        <v>Subiu</v>
       </c>
       <c r="D27">
         <v>1995</v>
@@ -907,9 +907,9 @@
       <c r="B28">
         <v>109.247925564181</v>
       </c>
-      <c r="C28">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="C28" t="str">
+        <f t="shared" si="0"/>
+        <v>Subiu</v>
       </c>
       <c r="D28">
         <v>3317</v>
@@ -925,9 +925,9 @@
       <c r="B29">
         <v>117.342167037574</v>
       </c>
-      <c r="C29">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="C29" t="str">
+        <f t="shared" si="0"/>
+        <v>Subiu</v>
       </c>
       <c r="D29">
         <v>4934</v>
@@ -943,9 +943,9 @@
       <c r="B30">
         <v>124.91242767799569</v>
       </c>
-      <c r="C30">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="C30" t="str">
+        <f t="shared" si="0"/>
+        <v>Subiu</v>
       </c>
       <c r="D30">
         <v>1815</v>
@@ -961,9 +961,9 @@
       <c r="B31">
         <v>132.48268831841699</v>
       </c>
-      <c r="C31">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="C31" t="str">
+        <f t="shared" si="0"/>
+        <v>Caiu</v>
       </c>
       <c r="D31">
         <v>-1304</v>

--- a/DataframeAcao.xlsx
+++ b/DataframeAcao.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="7">
   <si>
     <t>Preco</t>
   </si>
@@ -34,6 +34,12 @@
   </si>
   <si>
     <t>Dia</t>
+  </si>
+  <si>
+    <t>Subiu</t>
+  </si>
+  <si>
+    <t>Caiu</t>
   </si>
 </sst>
 </file>
@@ -439,9 +445,8 @@
       <c r="B2">
         <v>101.35844985184001</v>
       </c>
-      <c r="C2" t="str">
-        <f>IF(B3&gt;B2,"Subiu","Caiu")</f>
-        <v>Subiu</v>
+      <c r="C2" t="s">
+        <v>5</v>
       </c>
       <c r="D2">
         <v>4499</v>
@@ -457,9 +462,8 @@
       <c r="B3">
         <v>102.5061383899407</v>
       </c>
-      <c r="C3" t="str">
-        <f t="shared" ref="C3:C31" si="0">IF(B4&gt;B3,"Subiu","Caiu")</f>
-        <v>Subiu</v>
+      <c r="C3" t="s">
+        <v>5</v>
       </c>
       <c r="D3">
         <v>3556</v>
@@ -475,9 +479,8 @@
       <c r="B4">
         <v>104.5291682463488</v>
       </c>
-      <c r="C4" t="str">
-        <f t="shared" si="0"/>
-        <v>Subiu</v>
+      <c r="C4" t="s">
+        <v>5</v>
       </c>
       <c r="D4">
         <v>1775</v>
@@ -493,9 +496,8 @@
       <c r="B5">
         <v>104.7950148716254</v>
       </c>
-      <c r="C5" t="str">
-        <f t="shared" si="0"/>
-        <v>Subiu</v>
+      <c r="C5" t="s">
+        <v>5</v>
       </c>
       <c r="D5">
         <v>1034</v>
@@ -511,9 +513,8 @@
       <c r="B6">
         <v>105.0608779146763</v>
       </c>
-      <c r="C6" t="str">
-        <f t="shared" si="0"/>
-        <v>Subiu</v>
+      <c r="C6" t="s">
+        <v>5</v>
       </c>
       <c r="D6">
         <v>3253</v>
@@ -529,9 +530,8 @@
       <c r="B7">
         <v>107.1400907301836</v>
       </c>
-      <c r="C7" t="str">
-        <f t="shared" si="0"/>
-        <v>Subiu</v>
+      <c r="C7" t="s">
+        <v>5</v>
       </c>
       <c r="D7">
         <v>4152</v>
@@ -547,9 +547,8 @@
       <c r="B8">
         <v>108.4075254593366</v>
       </c>
-      <c r="C8" t="str">
-        <f t="shared" si="0"/>
-        <v>Subiu</v>
+      <c r="C8" t="s">
+        <v>5</v>
       </c>
       <c r="D8">
         <v>2955</v>
@@ -565,9 +564,8 @@
       <c r="B9">
         <v>108.4380510734016</v>
       </c>
-      <c r="C9" t="str">
-        <f t="shared" si="0"/>
-        <v>Subiu</v>
+      <c r="C9" t="s">
+        <v>5</v>
       </c>
       <c r="D9">
         <v>2585</v>
@@ -583,9 +581,8 @@
       <c r="B10">
         <v>109.4806111169876</v>
       </c>
-      <c r="C10" t="str">
-        <f t="shared" si="0"/>
-        <v>Subiu</v>
+      <c r="C10" t="s">
+        <v>5</v>
       </c>
       <c r="D10">
         <v>4943</v>
@@ -601,9 +598,8 @@
       <c r="B11">
         <v>109.5171934241751</v>
       </c>
-      <c r="C11" t="str">
-        <f t="shared" si="0"/>
-        <v>Subiu</v>
+      <c r="C11" t="s">
+        <v>5</v>
       </c>
       <c r="D11">
         <v>4459</v>
@@ -619,9 +615,8 @@
       <c r="B12">
         <v>109.5514636706048</v>
       </c>
-      <c r="C12" t="str">
-        <f t="shared" si="0"/>
-        <v>Subiu</v>
+      <c r="C12" t="s">
+        <v>5</v>
       </c>
       <c r="D12">
         <v>4073</v>
@@ -637,9 +632,8 @@
       <c r="B13">
         <v>110.2934259421709</v>
       </c>
-      <c r="C13" t="str">
-        <f t="shared" si="0"/>
-        <v>Caiu</v>
+      <c r="C13" t="s">
+        <v>5</v>
       </c>
       <c r="D13">
         <v>2021</v>
@@ -655,9 +649,8 @@
       <c r="B14">
         <v>108.8801456975131</v>
       </c>
-      <c r="C14" t="str">
-        <f t="shared" si="0"/>
-        <v>Caiu</v>
+      <c r="C14" t="s">
+        <v>6</v>
       </c>
       <c r="D14">
         <v>4461</v>
@@ -673,9 +666,8 @@
       <c r="B15">
         <v>107.655227865</v>
       </c>
-      <c r="C15" t="str">
-        <f t="shared" si="0"/>
-        <v>Caiu</v>
+      <c r="C15" t="s">
+        <v>6</v>
       </c>
       <c r="D15">
         <v>3613</v>
@@ -691,9 +683,8 @@
       <c r="B16">
         <v>107.5929403357591</v>
       </c>
-      <c r="C16" t="str">
-        <f t="shared" si="0"/>
-        <v>Caiu</v>
+      <c r="C16" t="s">
+        <v>6</v>
       </c>
       <c r="D16">
         <v>2129</v>
@@ -709,9 +700,8 @@
       <c r="B17">
         <v>107.0801092154247</v>
       </c>
-      <c r="C17" t="str">
-        <f t="shared" si="0"/>
-        <v>Subiu</v>
+      <c r="C17" t="s">
+        <v>6</v>
       </c>
       <c r="D17">
         <v>4843</v>
@@ -727,9 +717,8 @@
       <c r="B18">
         <v>107.8943565480199</v>
       </c>
-      <c r="C18" t="str">
-        <f t="shared" si="0"/>
-        <v>Caiu</v>
+      <c r="C18" t="s">
+        <v>5</v>
       </c>
       <c r="D18">
         <v>4893</v>
@@ -745,9 +734,8 @@
       <c r="B19">
         <v>107.4863324724987</v>
       </c>
-      <c r="C19" t="str">
-        <f t="shared" si="0"/>
-        <v>Caiu</v>
+      <c r="C19" t="s">
+        <v>6</v>
       </c>
       <c r="D19">
         <v>2500</v>
@@ -763,9 +751,8 @@
       <c r="B20">
         <v>106.5740287711634</v>
       </c>
-      <c r="C20" t="str">
-        <f t="shared" si="0"/>
-        <v>Subiu</v>
+      <c r="C20" t="s">
+        <v>6</v>
       </c>
       <c r="D20">
         <v>1702</v>
@@ -781,9 +768,8 @@
       <c r="B21">
         <v>108.53967754008499</v>
       </c>
-      <c r="C21" t="str">
-        <f t="shared" si="0"/>
-        <v>Subiu</v>
+      <c r="C21" t="s">
+        <v>5</v>
       </c>
       <c r="D21">
         <v>3449</v>
@@ -799,9 +785,8 @@
       <c r="B22">
         <v>108.81390123959839</v>
       </c>
-      <c r="C22" t="str">
-        <f t="shared" si="0"/>
-        <v>Subiu</v>
+      <c r="C22" t="s">
+        <v>5</v>
       </c>
       <c r="D22">
         <v>3777</v>
@@ -817,9 +802,8 @@
       <c r="B23">
         <v>109.3814294442864</v>
       </c>
-      <c r="C23" t="str">
-        <f t="shared" si="0"/>
-        <v>Caiu</v>
+      <c r="C23" t="s">
+        <v>5</v>
       </c>
       <c r="D23">
         <v>2579</v>
@@ -835,9 +819,8 @@
       <c r="B24">
         <v>108.4566812580729</v>
       </c>
-      <c r="C24" t="str">
-        <f t="shared" si="0"/>
-        <v>Caiu</v>
+      <c r="C24" t="s">
+        <v>6</v>
       </c>
       <c r="D24">
         <v>1161</v>
@@ -853,9 +836,8 @@
       <c r="B25">
         <v>108.4122985335477</v>
       </c>
-      <c r="C25" t="str">
-        <f t="shared" si="0"/>
-        <v>Subiu</v>
+      <c r="C25" t="s">
+        <v>6</v>
       </c>
       <c r="D25">
         <v>1201</v>
@@ -871,9 +853,8 @@
       <c r="B26">
         <v>109.0232211232576</v>
       </c>
-      <c r="C26" t="str">
-        <f t="shared" si="0"/>
-        <v>Caiu</v>
+      <c r="C26" t="s">
+        <v>5</v>
       </c>
       <c r="D26">
         <v>2981</v>
@@ -889,9 +870,8 @@
       <c r="B27">
         <v>108.3722275458353</v>
       </c>
-      <c r="C27" t="str">
-        <f t="shared" si="0"/>
-        <v>Subiu</v>
+      <c r="C27" t="s">
+        <v>6</v>
       </c>
       <c r="D27">
         <v>1995</v>
@@ -907,9 +887,8 @@
       <c r="B28">
         <v>109.247925564181</v>
       </c>
-      <c r="C28" t="str">
-        <f t="shared" si="0"/>
-        <v>Subiu</v>
+      <c r="C28" t="s">
+        <v>5</v>
       </c>
       <c r="D28">
         <v>3317</v>
@@ -925,9 +904,8 @@
       <c r="B29">
         <v>117.342167037574</v>
       </c>
-      <c r="C29" t="str">
-        <f t="shared" si="0"/>
-        <v>Subiu</v>
+      <c r="C29" t="s">
+        <v>5</v>
       </c>
       <c r="D29">
         <v>4934</v>
@@ -943,9 +921,8 @@
       <c r="B30">
         <v>124.91242767799569</v>
       </c>
-      <c r="C30" t="str">
-        <f t="shared" si="0"/>
-        <v>Subiu</v>
+      <c r="C30" t="s">
+        <v>5</v>
       </c>
       <c r="D30">
         <v>1815</v>
@@ -961,9 +938,8 @@
       <c r="B31">
         <v>132.48268831841699</v>
       </c>
-      <c r="C31" t="str">
-        <f t="shared" si="0"/>
-        <v>Caiu</v>
+      <c r="C31" t="s">
+        <v>5</v>
       </c>
       <c r="D31">
         <v>-1304</v>
